--- a/output/pdf_financials_xlsx/BKTS.xlsx
+++ b/output/pdf_financials_xlsx/BKTS.xlsx
@@ -2187,16 +2187,16 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>12.489931</v>
+        <v>14.821447</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>17.016022</v>
+        <v>17.561798</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>18.126053</v>
+        <v>21.06222</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>18.126053</v>
+        <v>21.06222</v>
       </c>
     </row>
     <row r="93">
@@ -3454,7 +3454,11 @@
           <t>Reserve for warrants (Note 11)</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr"/>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E12" t="inlineStr">
         <is>
           <t>-</t>
@@ -4132,7 +4136,11 @@
           <t>Reserve for warrants (Note 14)</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr"/>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E31" t="inlineStr">
         <is>
           <t>-</t>
@@ -4570,7 +4578,11 @@
           <t>Reserve for warrants (Note 15)</t>
         </is>
       </c>
-      <c r="D43" t="inlineStr"/>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E43" s="5" t="n">
         <v>2.331516</v>
       </c>

--- a/output/pdf_financials_xlsx/BKTS.xlsx
+++ b/output/pdf_financials_xlsx/BKTS.xlsx
@@ -639,13 +639,13 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>0.001457</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.003588</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.003651</v>
       </c>
       <c r="E12" s="3" t="n">
         <v>0</v>
@@ -942,13 +942,13 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-6.171224</v>
+        <v>-6.172681</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-4.991</v>
+        <v>-4.994588</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-3.798959</v>
+        <v>-3.80261</v>
       </c>
       <c r="E27" s="3" t="n">
         <v>-1.29719</v>
@@ -980,13 +980,13 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-6.171224</v>
+        <v>-6.172681</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-4.991</v>
+        <v>-4.994588</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-3.798959</v>
+        <v>-3.80261</v>
       </c>
       <c r="E29" s="3" t="n">
         <v>-1.29719</v>
@@ -999,13 +999,13 @@
         </is>
       </c>
       <c r="B30" s="3" t="n">
-        <v>-415.7307730654502</v>
+        <v>-415.8289253503707</v>
       </c>
       <c r="C30" s="3" t="n">
-        <v>-208.8310731933874</v>
+        <v>-208.9812006008444</v>
       </c>
       <c r="D30" s="3" t="n">
-        <v>-311.3602220114956</v>
+        <v>-311.659455609585</v>
       </c>
       <c r="E30" s="3" t="n">
         <v>-105.0343518094922</v>
@@ -1063,16 +1063,16 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.183623</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.059989</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.961138</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.150795</v>
       </c>
     </row>
     <row r="35">
@@ -1101,16 +1101,16 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.183623</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.059989</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.961138</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.150795</v>
       </c>
     </row>
     <row r="37">
@@ -1329,13 +1329,13 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.314062</v>
+        <v>0.130439</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.160694</v>
+        <v>0.100705</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>1.028162</v>
+        <v>0.067024</v>
       </c>
       <c r="E48" s="3" t="n">
         <v>0</v>
@@ -2785,10 +2785,10 @@
         </is>
       </c>
       <c r="B124" s="3" t="n">
-        <v>0</v>
+        <v>-0.874292</v>
       </c>
       <c r="C124" s="3" t="n">
-        <v>0</v>
+        <v>-0.298355</v>
       </c>
       <c r="D124" s="3" t="n">
         <v>0</v>
@@ -2804,10 +2804,10 @@
         </is>
       </c>
       <c r="B125" s="3" t="n">
-        <v>0</v>
+        <v>-0.874292</v>
       </c>
       <c r="C125" s="3" t="n">
-        <v>0</v>
+        <v>-0.298355</v>
       </c>
       <c r="D125" s="3" t="n">
         <v>0</v>
@@ -3096,7 +3096,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">
@@ -6154,7 +6154,11 @@
           <t>Lease payments</t>
         </is>
       </c>
-      <c r="D87" t="inlineStr"/>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E87" t="inlineStr">
         <is>
           <t>-</t>
@@ -6718,7 +6722,11 @@
           <t>Lease payments (Note 10)</t>
         </is>
       </c>
-      <c r="D103" t="inlineStr"/>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E103" s="5" t="n">
         <v>-0.874292</v>
       </c>
@@ -7560,7 +7568,7 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
@@ -8598,7 +8606,7 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E157" s="5" t="n">

--- a/output/pdf_financials_xlsx/BKTS.xlsx
+++ b/output/pdf_financials_xlsx/BKTS.xlsx
@@ -961,13 +961,13 @@
         </is>
       </c>
       <c r="B28" s="3" t="n">
-        <v>0</v>
+        <v>1.723125</v>
       </c>
       <c r="C28" s="3" t="n">
-        <v>0</v>
+        <v>1.571563</v>
       </c>
       <c r="D28" s="3" t="n">
-        <v>0</v>
+        <v>0.429001</v>
       </c>
       <c r="E28" s="3" t="n">
         <v>0</v>
@@ -980,13 +980,13 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-6.172681</v>
+        <v>-4.449556</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-4.994588</v>
+        <v>-3.423025</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-3.80261</v>
+        <v>-3.373609</v>
       </c>
       <c r="E29" s="3" t="n">
         <v>-1.29719</v>
@@ -999,13 +999,13 @@
         </is>
       </c>
       <c r="B30" s="3" t="n">
-        <v>-415.8289253503707</v>
+        <v>-299.7488594933537</v>
       </c>
       <c r="C30" s="3" t="n">
-        <v>-208.9812006008444</v>
+        <v>-143.2246011456211</v>
       </c>
       <c r="D30" s="3" t="n">
-        <v>-311.659455609585</v>
+        <v>-276.4988111795836</v>
       </c>
       <c r="E30" s="3" t="n">
         <v>-105.0343518094922</v>
@@ -2327,13 +2327,13 @@
         </is>
       </c>
       <c r="B100" s="3" t="n">
-        <v>0</v>
+        <v>1.723125</v>
       </c>
       <c r="C100" s="3" t="n">
-        <v>0</v>
+        <v>1.571563</v>
       </c>
       <c r="D100" s="3" t="n">
-        <v>0</v>
+        <v>0.429001</v>
       </c>
       <c r="E100" s="3" t="n">
         <v>0</v>
@@ -4794,7 +4794,11 @@
           <t>Depreciation of property and equipment</t>
         </is>
       </c>
-      <c r="D49" t="inlineStr"/>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E49" t="inlineStr">
         <is>
           <t>-</t>
@@ -5542,7 +5546,11 @@
           <t>Depreciation of property and equipment (Note 8)</t>
         </is>
       </c>
-      <c r="D70" t="inlineStr"/>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E70" t="inlineStr">
         <is>
           <t>-</t>
@@ -5750,7 +5758,11 @@
           <t>Depreciation of right-of-use assets</t>
         </is>
       </c>
-      <c r="D76" t="inlineStr"/>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E76" t="inlineStr">
         <is>
           <t>-</t>
@@ -6262,7 +6274,11 @@
           <t>Depreciation of property and equipment (Note 8)</t>
         </is>
       </c>
-      <c r="D90" t="inlineStr"/>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E90" s="5" t="n">
         <v>1.098056</v>
       </c>
@@ -6402,7 +6418,11 @@
           <t>Depreciation of right-of-use assets (Note 10)</t>
         </is>
       </c>
-      <c r="D94" t="inlineStr"/>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E94" s="5" t="n">
         <v>0.625069</v>
       </c>
@@ -7390,7 +7410,11 @@
           <t>Depreciation of property and equipment</t>
         </is>
       </c>
-      <c r="D122" t="inlineStr"/>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E122" t="inlineStr">
         <is>
           <t>-</t>
@@ -8398,7 +8422,11 @@
           <t>Depreciation of property and equipment (Note 8)</t>
         </is>
       </c>
-      <c r="D151" t="inlineStr"/>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E151" s="5" t="n">
         <v>1.098056</v>
       </c>
@@ -8498,7 +8526,11 @@
           <t>Depreciation of right-of-use assets</t>
         </is>
       </c>
-      <c r="D154" t="inlineStr"/>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E154" t="inlineStr">
         <is>
           <t>-</t>
@@ -9286,7 +9318,11 @@
           <t>Depreciation of right-of-use assets (Note 10)</t>
         </is>
       </c>
-      <c r="D176" t="inlineStr"/>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E176" s="5" t="n">
         <v>0.625069</v>
       </c>

--- a/output/pdf_financials_xlsx/BKTS.xlsx
+++ b/output/pdf_financials_xlsx/BKTS.xlsx
@@ -1645,16 +1645,16 @@
         </is>
       </c>
       <c r="B64" s="3" t="n">
-        <v>0</v>
+        <v>0.6590549999999999</v>
       </c>
       <c r="C64" s="3" t="n">
-        <v>0</v>
+        <v>1.736027</v>
       </c>
       <c r="D64" s="3" t="n">
-        <v>0</v>
+        <v>1.173507</v>
       </c>
       <c r="E64" s="3" t="n">
-        <v>0</v>
+        <v>1.029739</v>
       </c>
     </row>
     <row r="65">
@@ -1702,16 +1702,16 @@
         </is>
       </c>
       <c r="B67" s="3" t="n">
-        <v>0</v>
+        <v>0.256939</v>
       </c>
       <c r="C67" s="3" t="n">
-        <v>0</v>
+        <v>0.304676</v>
       </c>
       <c r="D67" s="3" t="n">
-        <v>0</v>
+        <v>0.157022</v>
       </c>
       <c r="E67" s="3" t="n">
-        <v>0</v>
+        <v>0.163157</v>
       </c>
     </row>
     <row r="68">
